--- a/plm python control/wrappers/multibeam parameters/plough/plough_MASTER.xlsx
+++ b/plm python control/wrappers/multibeam parameters/plough/plough_MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\plough\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0D55EA-CAB0-4D3C-A150-9CF8CDA861B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0B8690-B7DD-4EA9-8481-E14DDA6580C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17565" yWindow="1455" windowWidth="7275" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12435" yWindow="2265" windowWidth="9060" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="11">
   <si>
     <t>Beam A</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>Beam</t>
+  </si>
+  <si>
+    <t>HG10</t>
   </si>
   <si>
     <t>Grating period X (plm pix)</t>
@@ -47,9 +50,6 @@
   </si>
   <si>
     <t>Global amplitude</t>
-  </si>
-  <si>
-    <t>HG10</t>
   </si>
   <si>
     <t>HG</t>
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +404,6 @@
   <dimension ref="A2:D105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.85546875" customWidth="1"/>
     <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -416,7 +415,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -430,7 +429,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>10.55</v>
@@ -444,7 +443,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>138.32</v>
@@ -458,7 +457,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>10.412000000000001</v>
@@ -472,10 +471,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>86.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -486,10 +485,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -500,37 +499,37 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9">
-        <v>0.9</v>
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
     </row>
@@ -542,65 +541,65 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>1.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
         <v>0</v>
       </c>
     </row>
@@ -609,10 +608,10 @@
         <v>0</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>12.6</v>
@@ -623,10 +622,10 @@
         <v>0</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>10.8</v>
@@ -637,13 +636,13 @@
         <v>1</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>65.932000000000002</v>
+        <v>66.512</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -651,13 +650,13 @@
         <v>1</v>
       </c>
       <c r="B20">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>10.657500000000001</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -665,13 +664,13 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>82.6</v>
+        <v>79.400000000000006</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -679,10 +678,10 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -693,40 +692,40 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B24">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24">
-        <v>0.9</v>
+        <v>2</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B25">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="1">
         <v>1</v>
       </c>
     </row>
@@ -735,68 +734,68 @@
         <v>2</v>
       </c>
       <c r="B26">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="A27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="1">
+      <c r="A28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="1">
+      <c r="A29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30">
         <v>0</v>
       </c>
     </row>
@@ -805,10 +804,10 @@
         <v>0</v>
       </c>
       <c r="B32">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <v>12</v>
@@ -819,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="B33">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>11.25</v>
@@ -833,13 +832,13 @@
         <v>1</v>
       </c>
       <c r="B34">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>52.531999999999996</v>
+        <v>52.612000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -847,10 +846,10 @@
         <v>1</v>
       </c>
       <c r="B35">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>11.1</v>
@@ -861,13 +860,13 @@
         <v>0</v>
       </c>
       <c r="B36">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>73</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -875,13 +874,13 @@
         <v>1</v>
       </c>
       <c r="B37">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -889,40 +888,40 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B39">
-        <v>24</v>
-      </c>
-      <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39">
-        <v>0.8</v>
+        <v>3</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B40">
-        <v>24</v>
-      </c>
-      <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1">
         <v>1</v>
       </c>
     </row>
@@ -931,68 +930,68 @@
         <v>2</v>
       </c>
       <c r="B41">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="1">
+      <c r="A42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="1">
+      <c r="A43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="1">
+      <c r="A44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="1">
+      <c r="A45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45">
         <v>0</v>
       </c>
     </row>
@@ -1001,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="B47">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47">
         <v>11.6</v>
@@ -1015,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="B48">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48">
         <v>12.45064130278138</v>
@@ -1029,10 +1028,10 @@
         <v>1</v>
       </c>
       <c r="B49">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49">
         <v>45.692</v>
@@ -1043,10 +1042,10 @@
         <v>1</v>
       </c>
       <c r="B50">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>12.266999999999999</v>
@@ -1057,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="B51">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D51">
-        <v>76.2</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1071,13 +1070,13 @@
         <v>1</v>
       </c>
       <c r="B52">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1085,40 +1084,40 @@
         <v>2</v>
       </c>
       <c r="B53">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B54">
-        <v>27</v>
-      </c>
-      <c r="C54" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54">
-        <v>0.8</v>
+        <v>4</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B55">
-        <v>27</v>
-      </c>
-      <c r="C55" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1127,68 +1126,68 @@
         <v>2</v>
       </c>
       <c r="B56">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="1">
+      <c r="A57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="1">
+      <c r="A58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="1">
+      <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="A60" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60">
         <v>0</v>
       </c>
     </row>
@@ -1197,13 +1196,13 @@
         <v>0</v>
       </c>
       <c r="B62">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62">
-        <v>11.442834138486299</v>
+        <v>11.443</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1211,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="B63">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63">
-        <v>11.5901771336554</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1225,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="B64">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64">
         <v>43.392000000000003</v>
@@ -1239,10 +1238,10 @@
         <v>1</v>
       </c>
       <c r="B65">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D65">
         <v>11.423999999999999</v>
@@ -1253,13 +1252,13 @@
         <v>0</v>
       </c>
       <c r="B66">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D66">
-        <v>70.599999999999994</v>
+        <v>77.599999999999994</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1267,10 +1266,10 @@
         <v>1</v>
       </c>
       <c r="B67">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -1281,41 +1280,41 @@
         <v>2</v>
       </c>
       <c r="B68">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B69">
-        <v>32</v>
-      </c>
-      <c r="C69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69">
-        <v>0.8</v>
+        <v>5</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B70">
-        <v>32</v>
-      </c>
-      <c r="C70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70">
-        <v>1.1000000000000001</v>
+        <v>5</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1323,68 +1322,68 @@
         <v>2</v>
       </c>
       <c r="B71">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D72" s="1">
+      <c r="A72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72">
+        <v>5</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" s="1">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73">
+        <v>5</v>
+      </c>
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D74" s="1">
+      <c r="A74" t="s">
+        <v>1</v>
+      </c>
+      <c r="B74">
+        <v>5</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="1">
+      <c r="A75" t="s">
+        <v>1</v>
+      </c>
+      <c r="B75">
+        <v>5</v>
+      </c>
+      <c r="C75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75">
         <v>0</v>
       </c>
     </row>
@@ -1393,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="B77">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C77" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77">
         <v>10.6</v>
@@ -1407,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="B78">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C78" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D78">
         <v>13</v>
@@ -1421,10 +1420,10 @@
         <v>1</v>
       </c>
       <c r="B79">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C79" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79">
         <v>33.380000000000003</v>
@@ -1435,10 +1434,10 @@
         <v>1</v>
       </c>
       <c r="B80">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C80" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D80">
         <v>12.79</v>
@@ -1449,13 +1448,13 @@
         <v>0</v>
       </c>
       <c r="B81">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="B82">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C82" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -1477,40 +1476,40 @@
         <v>2</v>
       </c>
       <c r="B83">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C83" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B84">
-        <v>42</v>
-      </c>
-      <c r="C84" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84">
-        <v>0.9</v>
+        <v>6</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B85">
-        <v>42</v>
-      </c>
-      <c r="C85" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85">
+        <v>6</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1519,68 +1518,68 @@
         <v>2</v>
       </c>
       <c r="B86">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D87" s="1">
+      <c r="A87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87">
+        <v>6</v>
+      </c>
+      <c r="C87" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87">
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88" s="1">
+      <c r="A88" t="s">
+        <v>0</v>
+      </c>
+      <c r="B88">
+        <v>6</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88">
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D89" s="1">
+      <c r="A89" t="s">
+        <v>1</v>
+      </c>
+      <c r="B89">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89">
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D90" s="1">
+      <c r="A90" t="s">
+        <v>1</v>
+      </c>
+      <c r="B90">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90">
         <v>0</v>
       </c>
     </row>
@@ -1589,10 +1588,10 @@
         <v>0</v>
       </c>
       <c r="B92">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C92" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D92">
         <v>10.205</v>
@@ -1603,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="B93">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D93">
         <v>11.91111111111111</v>
@@ -1617,10 +1616,10 @@
         <v>1</v>
       </c>
       <c r="B94">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C94" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D94">
         <v>29.78</v>
@@ -1631,13 +1630,13 @@
         <v>1</v>
       </c>
       <c r="B95">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C95" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D95">
-        <v>11.718</v>
+        <v>11.731999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="B96">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D96">
         <v>66.8</v>
@@ -1659,13 +1658,13 @@
         <v>1</v>
       </c>
       <c r="B97">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C97" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,41 +1672,41 @@
         <v>2</v>
       </c>
       <c r="B98">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C98" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="A99" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B99">
-        <v>47</v>
-      </c>
-      <c r="C99" t="s">
-        <v>7</v>
-      </c>
-      <c r="D99">
-        <v>0.8</v>
+        <v>7</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B100">
-        <v>47</v>
-      </c>
-      <c r="C100" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100">
-        <v>1.1000000000000001</v>
+        <v>7</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -1715,68 +1714,68 @@
         <v>2</v>
       </c>
       <c r="B101">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" s="1">
+      <c r="A102" t="s">
+        <v>0</v>
+      </c>
+      <c r="B102">
+        <v>7</v>
+      </c>
+      <c r="C102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="1">
+      <c r="A103" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103">
+        <v>7</v>
+      </c>
+      <c r="C103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103">
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D104" s="1">
+      <c r="A104" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104">
+        <v>7</v>
+      </c>
+      <c r="C104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104">
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D105" s="1">
+      <c r="A105" t="s">
+        <v>1</v>
+      </c>
+      <c r="B105">
+        <v>7</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105">
         <v>0</v>
       </c>
     </row>

--- a/plm python control/wrappers/multibeam parameters/plough/plough_MASTER.xlsx
+++ b/plm python control/wrappers/multibeam parameters/plough/plough_MASTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\plough\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0B8690-B7DD-4EA9-8481-E14DDA6580C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877E993A-92EB-4331-9BA9-F21ECF82427E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12435" yWindow="2265" windowWidth="9060" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20640" yWindow="795" windowWidth="6810" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -446,7 +446,7 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>138.32</v>
+        <v>170.2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -460,7 +460,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>10.412000000000001</v>
+        <v>10.3825</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -474,7 +474,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>95</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -516,7 +516,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -530,7 +530,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">

--- a/plm python control/wrappers/multibeam parameters/plough/plough_MASTER.xlsx
+++ b/plm python control/wrappers/multibeam parameters/plough/plough_MASTER.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\plough\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877E993A-92EB-4331-9BA9-F21ECF82427E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8863BDFC-F67E-40D6-A44A-B8ECA5475D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20640" yWindow="795" windowWidth="6810" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20175" yWindow="795" windowWidth="7275" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -544,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -642,7 +655,7 @@
         <v>4</v>
       </c>
       <c r="D19">
-        <v>66.512</v>
+        <v>74.87</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -656,7 +669,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>10.66</v>
+        <v>10.625</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -670,7 +683,7 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>79.400000000000006</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -684,7 +697,7 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -712,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -740,7 +753,7 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -838,7 +851,7 @@
         <v>4</v>
       </c>
       <c r="D34">
-        <v>52.612000000000002</v>
+        <v>58.12</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -852,7 +865,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>11.1</v>
+        <v>11.0665</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -866,7 +879,7 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>78.8</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -880,7 +893,7 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -908,7 +921,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,7 +949,7 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1034,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="D49">
-        <v>45.692</v>
+        <v>49.911999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1048,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="D50">
-        <v>12.266999999999999</v>
+        <v>12.2315</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1062,7 +1075,7 @@
         <v>6</v>
       </c>
       <c r="D51">
-        <v>81.8</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1076,7 +1089,7 @@
         <v>6</v>
       </c>
       <c r="D52">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1104,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1132,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1230,7 +1243,7 @@
         <v>4</v>
       </c>
       <c r="D64">
-        <v>43.392000000000003</v>
+        <v>47.072000000000003</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1244,7 +1257,7 @@
         <v>5</v>
       </c>
       <c r="D65">
-        <v>11.423999999999999</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1258,7 +1271,8 @@
         <v>6</v>
       </c>
       <c r="D66">
-        <v>77.599999999999994</v>
+        <f>61.8-25</f>
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,7 +1286,7 @@
         <v>6</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1300,7 +1314,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1328,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1426,7 +1440,7 @@
         <v>4</v>
       </c>
       <c r="D79">
-        <v>33.380000000000003</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1440,7 +1454,7 @@
         <v>5</v>
       </c>
       <c r="D80">
-        <v>12.79</v>
+        <v>12.755000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1454,7 +1468,8 @@
         <v>6</v>
       </c>
       <c r="D81">
-        <v>75</v>
+        <f>15.6+25</f>
+        <v>40.6</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -1468,7 +1483,7 @@
         <v>6</v>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,7 +1511,7 @@
         <v>8</v>
       </c>
       <c r="D84" s="1">
-        <v>0</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,7 +1539,7 @@
         <v>9</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -1622,7 +1637,7 @@
         <v>4</v>
       </c>
       <c r="D94">
-        <v>29.78</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="D95">
-        <v>11.731999999999999</v>
+        <v>11.711499999999999</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,7 +1735,7 @@
         <v>9</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
